--- a/data/2026/cjsl/fall/lucky-soccer-academy-shining-stars-14-15.xlsx
+++ b/data/2026/cjsl/fall/lucky-soccer-academy-shining-stars-14-15.xlsx
@@ -78,7 +78,7 @@
     <col min="6" max="6" bestFit="1" customWidth="1" width="47.300000000000004"/>
     <col min="7" max="7" bestFit="1" customWidth="1" width="36.300000000000004"/>
     <col min="8" max="8" bestFit="1" customWidth="1" width="19.8"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" width="11.0"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" width="12.100000000000001"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -175,21 +175,21 @@
     </row>
     <row r="3">
       <c r="A3" s="0" t="n">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t>Saturday, September 26, 2026</t>
+          <t>Saturday, October 17, 2026</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t>15:00 EDT</t>
+          <t>14:30 EDT</t>
         </is>
       </c>
       <c r="D3" s="0" t="inlineStr">
         <is>
-          <t>Pelham Bay Soccer Club PBSC Elm - 2014-2015</t>
+          <t>Lucky Soccer Academy Shining Stars 14-15</t>
         </is>
       </c>
       <c r="E3" s="0" t="inlineStr">
@@ -199,12 +199,12 @@
       </c>
       <c r="F3" s="0" t="inlineStr">
         <is>
-          <t>Lucky Soccer Academy Shining Stars 14-15</t>
+          <t>Long Island CIty Youth Soccer Academy LIC Arsenal 2015/2014</t>
         </is>
       </c>
       <c r="G3" s="0" t="inlineStr">
         <is>
-          <t>Bronx Park East - Turf</t>
+          <t>Bill Brown Playground - 1</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
@@ -220,21 +220,21 @@
     </row>
     <row r="4">
       <c r="A4" s="0" t="n">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>Saturday, October 17, 2026</t>
+          <t>Sunday, October 25, 2026</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>14:30 EDT</t>
+          <t>11:40 EDT</t>
         </is>
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t>Lucky Soccer Academy Shining Stars 14-15</t>
+          <t>GOAT Youth Soccer Academy Boys 2014/2015</t>
         </is>
       </c>
       <c r="E4" s="0" t="inlineStr">
@@ -244,12 +244,12 @@
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>Long Island CIty Youth Soccer Academy LIC Arsenal 2015/2014</t>
+          <t>Lucky Soccer Academy Shining Stars 14-15</t>
         </is>
       </c>
       <c r="G4" s="0" t="inlineStr">
         <is>
-          <t>Bill Brown Playground - 1</t>
+          <t>Randall's Island - 73</t>
         </is>
       </c>
       <c r="H4" s="0" t="inlineStr">
@@ -259,27 +259,27 @@
       </c>
       <c r="I4" s="0" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t>Sunday, October 25, 2026</t>
+          <t>Saturday, October 31, 2026</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>11:40 EDT</t>
+          <t>14:30 EDT</t>
         </is>
       </c>
       <c r="D5" s="0" t="inlineStr">
         <is>
-          <t>GOAT Youth Soccer Academy Boys 2014/2015</t>
+          <t>Lucky Soccer Academy Shining Stars 14-15</t>
         </is>
       </c>
       <c r="E5" s="0" t="inlineStr">
@@ -289,12 +289,12 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>Lucky Soccer Academy Shining Stars 14-15</t>
+          <t>Kickers Jr. of Southeast Queens BOYS (2014-2015) FALCONS</t>
         </is>
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t>Randall's Island - 73</t>
+          <t>Bill Brown Playground - 1</t>
         </is>
       </c>
       <c r="H5" s="0" t="inlineStr">
@@ -304,27 +304,27 @@
       </c>
       <c r="I5" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="n">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t>Saturday, October 31, 2026</t>
+          <t>Saturday, November  7, 2026</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>14:30 EDT</t>
+          <t/>
         </is>
       </c>
       <c r="D6" s="0" t="inlineStr">
         <is>
-          <t>Lucky Soccer Academy Shining Stars 14-15</t>
+          <t>Soccer Stars United Equator 2014/2015</t>
         </is>
       </c>
       <c r="E6" s="0" t="inlineStr">
@@ -334,12 +334,12 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>Kickers Jr. of Southeast Queens BOYS (2014-2015) FALCONS</t>
+          <t>Lucky Soccer Academy Shining Stars 14-15</t>
         </is>
       </c>
       <c r="G6" s="0" t="inlineStr">
         <is>
-          <t>Bill Brown Playground - 1</t>
+          <t/>
         </is>
       </c>
       <c r="H6" s="0" t="inlineStr">
@@ -347,29 +347,25 @@
           <t>U12 (9v9) - D4 Metro</t>
         </is>
       </c>
-      <c r="I6" s="0" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
+      <c r="I6" s="0"/>
     </row>
     <row r="7">
       <c r="A7" s="0" t="n">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t>Saturday, November  7, 2026</t>
+          <t>Saturday, November 14, 2026</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>14:30 EST</t>
         </is>
       </c>
       <c r="D7" s="0" t="inlineStr">
         <is>
-          <t>Soccer Stars United Equator 2014/2015</t>
+          <t>Lucky Soccer Academy Shining Stars 14-15</t>
         </is>
       </c>
       <c r="E7" s="0" t="inlineStr">
@@ -379,12 +375,12 @@
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>Lucky Soccer Academy Shining Stars 14-15</t>
+          <t>Pelham Bay Soccer Club PBSC Elm - 2014-2015</t>
         </is>
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Bill Brown Playground - 1</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
@@ -392,25 +388,29 @@
           <t>U12 (9v9) - D4 Metro</t>
         </is>
       </c>
-      <c r="I7" s="0"/>
+      <c r="I7" s="0" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="n">
-        <v>414</v>
+        <v>396</v>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t>Saturday, November 14, 2026</t>
+          <t>Saturday, November 21, 2026</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>14:30 EST</t>
+          <t>14:00 EST</t>
         </is>
       </c>
       <c r="D8" s="0" t="inlineStr">
         <is>
-          <t>Lucky Soccer Academy Shining Stars 14-15</t>
+          <t>Pelham Bay Soccer Club PBSC Elm - 2014-2015</t>
         </is>
       </c>
       <c r="E8" s="0" t="inlineStr">
@@ -420,12 +420,12 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>Pelham Bay Soccer Club PBSC Elm - 2014-2015</t>
+          <t>Lucky Soccer Academy Shining Stars 14-15</t>
         </is>
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t>Bill Brown Playground - 1</t>
+          <t>Bronx Park East - Turf</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
@@ -435,7 +435,7 @@
       </c>
       <c r="I8" s="0" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Rescheduled</t>
         </is>
       </c>
     </row>

--- a/data/2026/cjsl/fall/lucky-soccer-academy-shining-stars-14-15.xlsx
+++ b/data/2026/cjsl/fall/lucky-soccer-academy-shining-stars-14-15.xlsx
@@ -73,7 +73,7 @@
     <col min="1" max="1" bestFit="1" customWidth="1" width="7.700000000000001"/>
     <col min="2" max="2" bestFit="1" customWidth="1" width="27.500000000000004"/>
     <col min="3" max="3" bestFit="1" customWidth="1" width="13.200000000000001"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" width="44.0"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" width="47.300000000000004"/>
     <col min="5" max="5" bestFit="1" customWidth="1" width="7.700000000000001"/>
     <col min="6" max="6" bestFit="1" customWidth="1" width="47.300000000000004"/>
     <col min="7" max="7" bestFit="1" customWidth="1" width="36.300000000000004"/>
@@ -324,7 +324,7 @@
       </c>
       <c r="D6" s="0" t="inlineStr">
         <is>
-          <t>Soccer Stars United Equator 2014/2015</t>
+          <t>Soccer Stars United Met Oval - SSU Blue 2014/2015 (Equator)</t>
         </is>
       </c>
       <c r="E6" s="0" t="inlineStr">

--- a/data/2026/cjsl/fall/lucky-soccer-academy-shining-stars-14-15.xlsx
+++ b/data/2026/cjsl/fall/lucky-soccer-academy-shining-stars-14-15.xlsx
@@ -194,7 +194,7 @@
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3 - 1</t>
         </is>
       </c>
       <c r="F3" s="0" t="inlineStr">
@@ -224,12 +224,12 @@
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>Sunday, October 25, 2026</t>
+          <t>Saturday, October 24, 2026</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>11:40 EDT</t>
+          <t>14:30 EDT</t>
         </is>
       </c>
       <c r="D4" s="0" t="inlineStr">
@@ -249,7 +249,7 @@
       </c>
       <c r="G4" s="0" t="inlineStr">
         <is>
-          <t>Randall's Island - 73</t>
+          <t>Astoria Park - Soccer Field</t>
         </is>
       </c>
       <c r="H4" s="0" t="inlineStr">
@@ -259,7 +259,7 @@
       </c>
       <c r="I4" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Rescheduled</t>
         </is>
       </c>
     </row>

--- a/data/2026/cjsl/fall/lucky-soccer-academy-shining-stars-14-15.xlsx
+++ b/data/2026/cjsl/fall/lucky-soccer-academy-shining-stars-14-15.xlsx
@@ -239,7 +239,7 @@
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4 - 3</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">
@@ -259,7 +259,7 @@
       </c>
       <c r="I4" s="0" t="inlineStr">
         <is>
-          <t>Rescheduled</t>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
